--- a/tourism_data.xlsx
+++ b/tourism_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hacettepeedutr-my.sharepoint.com/personal/basaryilmaz_hacettepe_edu_tr/Documents/Masaüstü/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hacettepeedutr-my.sharepoint.com/personal/basaryilmaz_hacettepe_edu_tr/Documents/Belgeler/GitHub/emu430-fall2024-team-flynomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="277" documentId="8_{0BCEBB3A-C941-4A17-8EAD-6823A86F6083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF6B14BF-2546-4A1E-B183-76B38AF4EF2B}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="8_{0BCEBB3A-C941-4A17-8EAD-6823A86F6083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{875D6AE1-2726-4910-AC79-5D78E061E535}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{051D5308-2083-B043-8BC2-51223AE808D8}"/>
   </bookViews>
@@ -272,10 +272,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18726,11 +18722,11 @@
         <v>29</v>
       </c>
       <c r="F674" s="9">
-        <v>5776477</v>
+        <v>1792577</v>
       </c>
       <c r="G674" s="9">
-        <f t="shared" si="56"/>
-        <v>4111906</v>
+        <f>F674-F673</f>
+        <v>128006</v>
       </c>
       <c r="H674" s="5">
         <v>13.52849565</v>
